--- a/data/trans_camb/P19C06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,5</t>
+          <t>-1,0; 0,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,2</t>
+          <t>-0,66; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,6</t>
+          <t>-0,94; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,34</t>
+          <t>-0,16; 2,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,77</t>
+          <t>-0,6; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,97</t>
+          <t>-0,83; 1,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,12</t>
+          <t>-0,37; 1,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,08</t>
+          <t>-0,37; 1,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,63</t>
+          <t>-0,51; 0,7</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 977,87</t>
+          <t>-36,17; 879,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 786,0</t>
+          <t>-67,56; 771,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 472,37</t>
+          <t>-68,77; 523,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 414,75</t>
+          <t>-43,03; 417,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 369,88</t>
+          <t>-56,23; 483,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 246,69</t>
+          <t>-58,53; 351,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,3</t>
+          <t>-1,29; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,73</t>
+          <t>-1,65; 0,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,09</t>
+          <t>-1,76; 1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,09</t>
+          <t>-1,24; 1,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,3</t>
+          <t>-1,84; 0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,89</t>
+          <t>-1,22; 0,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,91</t>
+          <t>-0,91; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,23</t>
+          <t>-1,3; 0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,64</t>
+          <t>-1,15; 0,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 160,98</t>
+          <t>-61,39; 208,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 90,82</t>
+          <t>-73,48; 118,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 139,07</t>
+          <t>-82,59; 168,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,83; 167,88</t>
+          <t>-67,74; 146,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 60,93</t>
+          <t>-85,77; 61,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,18; 119,46</t>
+          <t>-62,98; 148,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 100,54</t>
+          <t>-50,17; 80,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 31,14</t>
+          <t>-70,56; 22,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 65,87</t>
+          <t>-61,67; 70,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,89</t>
+          <t>-1,14; 0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,69</t>
+          <t>-0,32; 2,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,61</t>
+          <t>-1,18; 0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,54</t>
+          <t>-1,2; 1,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,58</t>
+          <t>-1,89; 0,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,53</t>
+          <t>-1,91; 0,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,9</t>
+          <t>-0,89; 0,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,18</t>
+          <t>-0,87; 1,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,39</t>
+          <t>-1,29; 0,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,18; 286,57</t>
+          <t>-82,11; 282,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 550,44</t>
+          <t>-46,18; 822,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 193,25</t>
+          <t>-87,75; 242,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 193,9</t>
+          <t>-60,71; 203,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,22; 87,42</t>
+          <t>-83,39; 92,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 74,79</t>
+          <t>-77,05; 73,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 110,45</t>
+          <t>-55,11; 122,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 174,71</t>
+          <t>-53,67; 152,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 58,66</t>
+          <t>-70,34; 40,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,86</t>
+          <t>-1,28; 0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,06</t>
+          <t>-1,34; 1,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,52</t>
+          <t>-1,5; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,3</t>
+          <t>-0,7; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,89</t>
+          <t>0,27; 2,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,86</t>
+          <t>-0,9; 0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,77</t>
+          <t>-0,67; 0,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,62</t>
+          <t>-0,07; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,47</t>
+          <t>-0,85; 0,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 116,82</t>
+          <t>-71,18; 139,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 154,51</t>
+          <t>-68,58; 141,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,66; 74,92</t>
+          <t>-77,25; 95,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 256,86</t>
+          <t>-53,82; 292,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 639,81</t>
+          <t>3,56; 503,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 185,48</t>
+          <t>-55,59; 171,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 104,92</t>
+          <t>-42,84; 108,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 192,5</t>
+          <t>-8,72; 205,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,82; 58,27</t>
+          <t>-54,02; 64,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,44</t>
+          <t>-0,66; 0,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,72</t>
+          <t>-0,53; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,3</t>
+          <t>-0,84; 0,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,91</t>
+          <t>-0,27; 0,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,74</t>
+          <t>-0,37; 0,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,38</t>
+          <t>-0,6; 0,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,45</t>
+          <t>-0,31; 0,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,55</t>
+          <t>-0,27; 0,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,27</t>
+          <t>-0,54; 0,21</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 54,42</t>
+          <t>-47,05; 65,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 92,43</t>
+          <t>-39,19; 82,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 42,57</t>
+          <t>-58,94; 44,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 108,3</t>
+          <t>-20,29; 107,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 86,53</t>
+          <t>-26,25; 91,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 43,48</t>
+          <t>-41,72; 53,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 48,82</t>
+          <t>-23,62; 54,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 59,02</t>
+          <t>-20,43; 64,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 31,47</t>
+          <t>-42,23; 22,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,44</t>
+          <t>-1,01; 0,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,4</t>
+          <t>-0,81; 1,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,55</t>
+          <t>-0,95; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,4</t>
+          <t>-0,19; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,82</t>
+          <t>-0,5; 1,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,09</t>
+          <t>-0,68; 1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,15</t>
+          <t>-0,3; 1,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,2</t>
+          <t>-0,41; 1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,7</t>
+          <t>-0,49; 0,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,78%</t>
+          <t>-12,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 879,51</t>
+          <t>-29,09; 1199,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 771,74</t>
+          <t>-59,06; 941,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 523,39</t>
+          <t>-57,33; 581,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 417,99</t>
+          <t>-44,58; 438,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 483,9</t>
+          <t>-52,88; 414,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 351,95</t>
+          <t>-57,04; 297,56</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,42</t>
+          <t>-1,32; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,83</t>
+          <t>-1,65; 0,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,16</t>
+          <t>-1,54; 0,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,0</t>
+          <t>-1,28; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,32</t>
+          <t>-1,74; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,94</t>
+          <t>-1,46; 0,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,8</t>
+          <t>-0,87; 0,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,19</t>
+          <t>-1,26; 0,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,68</t>
+          <t>-1,09; 0,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-27,05%</t>
+          <t>-28,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,57%</t>
+          <t>-20,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,58%</t>
+          <t>-24,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 208,45</t>
+          <t>-60,45; 153,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 118,4</t>
+          <t>-74,81; 84,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 168,13</t>
+          <t>-74,72; 77,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 146,28</t>
+          <t>-63,73; 166,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 61,29</t>
+          <t>-83,22; 49,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 148,57</t>
+          <t>-68,07; 94,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 80,88</t>
+          <t>-48,24; 86,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 22,68</t>
+          <t>-67,63; 30,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,67; 70,22</t>
+          <t>-58,86; 62,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,89</t>
+          <t>-1,12; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,77</t>
+          <t>-0,37; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,69</t>
+          <t>-1,28; 0,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,63</t>
+          <t>-1,16; 1,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,51</t>
+          <t>-1,87; 0,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,51</t>
+          <t>-1,55; 0,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,93</t>
+          <t>-0,73; 1,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,13</t>
+          <t>-0,79; 1,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,29</t>
+          <t>-1,0; 0,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-23,05%</t>
+          <t>-28,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-34,0%</t>
+          <t>-14,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,71%</t>
+          <t>-19,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,11; 282,6</t>
+          <t>-86,68; 301,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 822,25</t>
+          <t>-49,7; 645,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 242,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 203,21</t>
+          <t>-58,0; 184,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 92,41</t>
+          <t>-85,64; 89,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,05; 73,47</t>
+          <t>-67,44; 114,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 122,02</t>
+          <t>-46,83; 145,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 152,14</t>
+          <t>-51,48; 141,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 40,06</t>
+          <t>-59,96; 67,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,97</t>
+          <t>-1,27; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,12</t>
+          <t>-1,21; 1,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,55</t>
+          <t>-1,62; 0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,34</t>
+          <t>-0,73; 1,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,75</t>
+          <t>0,24; 2,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,82</t>
+          <t>-0,76; 0,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,82</t>
+          <t>-0,71; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,63</t>
+          <t>-0,13; 1,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,48</t>
+          <t>-0,83; 0,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,99%</t>
+          <t>-36,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,89%</t>
+          <t>-14,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 139,9</t>
+          <t>-66,26; 152,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 141,92</t>
+          <t>-64,84; 170,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,25; 95,24</t>
+          <t>-77,61; 77,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,82; 292,8</t>
+          <t>-54,46; 246,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 503,59</t>
+          <t>6,25; 524,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 171,63</t>
+          <t>-49,04; 200,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 108,73</t>
+          <t>-47,42; 104,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 205,31</t>
+          <t>-12,96; 207,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 64,69</t>
+          <t>-55,55; 61,39</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,47</t>
+          <t>-0,69; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,68</t>
+          <t>-0,52; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,3</t>
+          <t>-0,85; 0,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,91</t>
+          <t>-0,29; 0,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,78</t>
+          <t>-0,37; 0,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,44</t>
+          <t>-0,55; 0,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,51</t>
+          <t>-0,32; 0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,58</t>
+          <t>-0,27; 0,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,21</t>
+          <t>-0,54; 0,18</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-24,4%</t>
+          <t>-29,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-3,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-15,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 65,45</t>
+          <t>-49,15; 57,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 82,75</t>
+          <t>-39,22; 80,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 44,67</t>
+          <t>-61,84; 27,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 107,56</t>
+          <t>-22,06; 101,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 91,49</t>
+          <t>-26,75; 100,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 53,12</t>
+          <t>-38,07; 54,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 54,46</t>
+          <t>-25,54; 55,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 64,77</t>
+          <t>-20,3; 63,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 22,38</t>
+          <t>-39,84; 20,75</t>
         </is>
       </c>
     </row>
